--- a/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,16 +621,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -640,12 +635,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -665,7 +660,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -680,7 +675,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -690,17 +685,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -713,7 +708,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,12 +718,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -748,7 +743,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -763,7 +758,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -773,17 +768,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -792,11 +787,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -875,16 +875,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -894,12 +889,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -919,7 +914,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -934,7 +929,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -944,17 +939,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -963,11 +958,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1115,17 +1115,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1198,17 +1198,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1305,11 +1305,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1319,12 +1324,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1344,7 +1349,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1359,7 +1364,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1369,17 +1374,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1397,7 +1402,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1407,12 +1412,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1457,17 +1462,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1476,12 +1481,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1740,12 +1740,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1759,12 +1754,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1784,7 +1779,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1799,7 +1794,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1809,17 +1804,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1828,16 +1823,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1847,12 +1837,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1872,7 +1862,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1902,12 +1892,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1930,12 +1920,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1955,7 +1945,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1970,7 +1960,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1980,17 +1970,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1999,16 +1989,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2018,12 +2003,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2043,7 +2028,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2058,7 +2043,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2068,17 +2053,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2096,7 +2081,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2106,12 +2091,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2131,7 +2116,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2146,7 +2131,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2156,17 +2141,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2175,16 +2160,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2194,12 +2174,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2219,7 +2199,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2249,12 +2229,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2282,12 +2262,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2307,7 +2287,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2337,12 +2317,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2365,12 +2345,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2390,7 +2370,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2405,7 +2385,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2415,17 +2395,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2434,11 +2414,16 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2448,12 +2433,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2473,7 +2458,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2488,7 +2473,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2498,17 +2483,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2517,16 +2502,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2536,12 +2516,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2561,7 +2541,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2576,7 +2556,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2586,17 +2566,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2605,16 +2585,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2624,12 +2599,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2649,7 +2624,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2679,12 +2654,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2693,7 +2668,12 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2707,12 +2687,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2732,7 +2712,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2747,7 +2727,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2757,17 +2737,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2776,16 +2756,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2795,12 +2770,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2820,7 +2795,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2835,7 +2810,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2845,17 +2820,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2864,16 +2839,16 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>6,7,8,9,17,18</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2883,12 +2858,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2908,7 +2883,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2923,7 +2898,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2933,17 +2908,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2952,11 +2927,16 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2966,12 +2946,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2991,7 +2971,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3021,12 +3001,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3049,12 +3029,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3074,7 +3054,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3089,7 +3069,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3099,17 +3079,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3118,16 +3098,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3137,12 +3112,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3162,7 +3137,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3177,7 +3152,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3187,17 +3162,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3206,11 +3181,16 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>9,10</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3220,12 +3200,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3245,7 +3225,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3275,12 +3255,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3289,12 +3269,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3308,12 +3283,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3333,7 +3308,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3358,17 +3333,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3396,12 +3371,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3421,7 +3396,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3436,7 +3411,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3446,17 +3421,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3465,11 +3440,16 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3479,12 +3459,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3504,7 +3484,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3519,7 +3499,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3529,17 +3509,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3548,16 +3528,16 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3567,12 +3547,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3592,7 +3572,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3622,12 +3602,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3636,7 +3616,12 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3650,12 +3635,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3675,7 +3660,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3690,7 +3675,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3700,17 +3685,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3719,16 +3704,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3738,12 +3718,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3763,7 +3743,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3778,7 +3758,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3788,17 +3768,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3807,16 +3787,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3826,12 +3801,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3851,7 +3826,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3866,7 +3841,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3876,17 +3851,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3895,16 +3870,16 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3914,12 +3889,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3939,7 +3914,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3964,17 +3939,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3983,11 +3958,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4002,12 +3977,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4027,7 +4002,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4042,7 +4017,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4052,17 +4027,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4071,16 +4046,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4090,12 +4060,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4115,7 +4085,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4130,7 +4100,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4140,17 +4110,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4159,11 +4129,16 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4173,12 +4148,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4198,7 +4173,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4213,7 +4188,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4223,17 +4198,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4251,7 +4226,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4261,12 +4236,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4286,7 +4261,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4301,7 +4276,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4311,17 +4286,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4330,11 +4305,16 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4344,12 +4324,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4369,7 +4349,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4384,7 +4364,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4394,17 +4374,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4422,7 +4402,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4432,12 +4412,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4457,7 +4437,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4482,17 +4462,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4515,12 +4495,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4540,7 +4520,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4555,7 +4535,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4565,17 +4545,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4584,16 +4564,16 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4603,12 +4583,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4628,7 +4608,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4643,7 +4623,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4653,17 +4633,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4681,7 +4661,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4691,12 +4671,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4716,7 +4696,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4731,7 +4711,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4741,17 +4721,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4760,16 +4740,16 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4779,12 +4759,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4804,7 +4784,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4829,17 +4809,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4848,11 +4828,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4867,12 +4847,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4892,7 +4872,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4907,7 +4887,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4917,17 +4897,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4936,16 +4916,16 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4955,12 +4935,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4980,7 +4960,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4995,7 +4975,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5005,17 +4985,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5024,11 +5004,16 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5038,12 +5023,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5063,7 +5048,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5078,7 +5063,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5088,17 +5073,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5107,16 +5092,11 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5126,12 +5106,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5151,7 +5131,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5166,7 +5146,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5176,17 +5156,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5204,7 +5184,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5214,12 +5194,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5239,7 +5219,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5254,7 +5234,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5264,17 +5244,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5283,11 +5263,16 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+        </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5297,12 +5282,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5322,7 +5307,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5337,7 +5322,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5347,17 +5332,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5366,16 +5351,11 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5385,12 +5365,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5410,7 +5390,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5425,7 +5405,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5435,17 +5415,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5454,16 +5434,16 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5473,12 +5453,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5498,7 +5478,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5513,7 +5493,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5523,17 +5503,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5542,11 +5522,16 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5556,12 +5541,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5581,7 +5566,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5611,12 +5596,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5625,7 +5610,12 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -5639,12 +5629,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5664,7 +5654,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5679,7 +5669,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5689,17 +5679,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5708,11 +5698,16 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5722,12 +5717,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5747,7 +5742,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5762,7 +5757,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5772,17 +5767,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5800,7 +5795,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5810,12 +5805,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5835,7 +5830,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5850,7 +5845,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5860,17 +5855,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5888,7 +5883,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5898,12 +5893,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5923,7 +5918,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5938,7 +5933,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5948,17 +5943,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5971,30 +5966,1159 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>zhangxuqing</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>张旭青</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>liyixin</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>李奕昕</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>liyixin</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>李奕昕</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>lvzhenyang</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>吕禛杨</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>lvzhenyang</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>吕禛杨</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>fengyifan01</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>冯一帆</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>22,23</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>fengyifan01</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>冯一帆</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>zhangjing03</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>张菁</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>zhangjing03</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>张菁</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>zhangxinyu01</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>张鑫禹</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>zhangxinyu01</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>张鑫禹</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>liuxiaosong</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>刘晓松</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>liuxiaosong</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>刘晓松</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>yangpengfei</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>杨鹏飞</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>yangpengfei</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>杨鹏飞</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>caotianao</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>曹添傲</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>caotianao</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>曹添傲</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>长期班</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>曹晓雨</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>caoxiaoyu</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>曹晓雨</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>caoxiaoyu</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>曹晓雨</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>weixiaodi</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>卫晓迪</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>weixiaodi</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>卫晓迪</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>limengyao03</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>李梦瑶</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>limengyao03</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>李梦瑶</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>anyixuan</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>安怡宣</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>anyixuan</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>安怡宣</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -6011,7 +7135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6059,17 +7183,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -6080,22 +7204,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -6111,17 +7235,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.4615384615384616</v>
       </c>
     </row>
     <row r="5">
@@ -6132,22 +7256,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="6">
@@ -6163,17 +7287,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="7">
@@ -6184,22 +7308,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.4444444444444444</v>
+      <c r="F8" t="n">
+        <v>0.1904761904761905</v>
       </c>
     </row>
   </sheetData>
@@ -6213,7 +7363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6306,110 +7456,110 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>曹晓雨</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>重装五组</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="E4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>0.8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>初一 汇总</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H4" s="5" t="n">
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="K4" s="6" t="n">
+      <c r="J5" s="6" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>0.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.4615384615384616</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -6425,110 +7575,110 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>重装九组</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="E7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="H7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>初三 汇总</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="n">
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="E8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0.7777777777777778</v>
+      <c r="H8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -6544,147 +7694,151 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>9</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>9</v>
       </c>
       <c r="H9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>初二 汇总</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="n">
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F11" s="6" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>0.7333333333333333</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>新兵营-出</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3" t="n">
+      <c r="D12" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I11" s="3" t="n">
+      <c r="F12" s="4" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>0.5555555555555556</v>
+      <c r="J12" s="4" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="13">
@@ -6695,33 +7849,70 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>初中 汇总</t>
+          <t>新兵营 汇总</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.6825396825396826</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.6744186046511628</v>
+        <v>0.4545454545454545</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.3552631578947368</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.6052631578947368</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0.6521739130434783</v>
       </c>
     </row>
   </sheetData>
@@ -6738,7 +7929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6801,7 +7992,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6852,7 +8043,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6903,7 +8094,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6954,7 +8145,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7005,7 +8196,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7056,7 +8247,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7107,7 +8298,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7158,7 +8349,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7209,7 +8400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7260,7 +8451,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7311,7 +8502,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7362,7 +8553,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7413,7 +8604,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7464,7 +8655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7515,7 +8706,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7566,7 +8757,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7617,7 +8808,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7668,7 +8859,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7719,7 +8910,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7770,7 +8961,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7821,7 +9012,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7872,7 +9063,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7923,7 +9114,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7974,7 +9165,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8025,7 +9216,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8076,7 +9267,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8127,7 +9318,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8178,7 +9369,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8229,7 +9420,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8280,7 +9471,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8331,7 +9522,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8382,7 +9573,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8407,19 +9598,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8433,7 +9624,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8458,19 +9649,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -8484,7 +9675,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8509,19 +9700,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -8535,7 +9726,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8560,19 +9751,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -8586,7 +9777,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8601,22 +9792,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -8637,7 +9828,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8662,12 +9853,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -8688,7 +9879,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8713,12 +9904,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -8739,7 +9930,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8764,12 +9955,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -8790,7 +9981,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8815,12 +10006,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -8841,7 +10032,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8866,19 +10057,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -8892,7 +10083,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8917,19 +10108,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="H43" t="n">
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -8943,7 +10134,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8968,19 +10159,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="H44" t="n">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -8994,7 +10185,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9019,19 +10210,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -9045,7 +10236,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9065,17 +10256,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -9096,7 +10287,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9121,12 +10312,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -9147,7 +10338,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9172,19 +10363,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -9198,7 +10389,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9223,19 +10414,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -9249,7 +10440,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9274,19 +10465,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -9300,7 +10491,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9325,16 +10516,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -9351,7 +10542,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9376,19 +10567,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -9402,7 +10593,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9427,19 +10618,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -9453,7 +10644,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9478,12 +10669,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -9504,7 +10695,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9519,26 +10710,26 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -9555,7 +10746,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9580,19 +10771,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -9606,7 +10797,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9657,7 +10848,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9682,16 +10873,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -9708,7 +10899,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9733,12 +10924,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -9759,7 +10950,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9784,12 +10975,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -9810,7 +11001,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -9835,19 +11026,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -9861,7 +11052,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9886,19 +11077,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -9912,7 +11103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9937,26 +11128,383 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>wangxuyang01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>王旭炀</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
         <v>1</v>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>yangzhijie01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>杨志杰</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>zhangbaohua01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>张宝华</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>zhangbingxin</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>张冰心</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>zhangjing03</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>张菁</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>zhangxinchi</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>张心驰</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>zhangying04</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>张迎</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
         <v>23</v>
       </c>
     </row>
@@ -9971,7 +11519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10029,23 +11577,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -10056,28 +11601,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -10093,23 +11638,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
         <v>6</v>
       </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -10120,28 +11665,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="6">
@@ -10157,23 +11702,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="7">
@@ -10184,28 +11729,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.5555555555555556</v>
+      <c r="G8" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4545454545454545</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -7382,7 +7382,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 9月14日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 9月16日</t>
         </is>
       </c>
     </row>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,11 +573,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,11 +621,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -635,12 +640,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -656,11 +661,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -675,7 +680,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -685,17 +690,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -704,11 +709,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -718,12 +728,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -739,11 +749,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -773,12 +783,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -806,12 +816,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -827,11 +837,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -856,17 +866,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -875,7 +885,12 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -889,12 +904,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -910,11 +925,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -929,7 +944,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -939,17 +954,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -958,16 +973,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -977,12 +987,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -998,11 +1008,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1017,7 +1027,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1027,17 +1037,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1046,16 +1056,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1065,12 +1070,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1086,11 +1091,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1105,7 +1110,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1115,17 +1120,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1134,11 +1139,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1148,12 +1158,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1169,11 +1179,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1188,7 +1198,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1198,17 +1208,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1226,7 +1236,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1236,12 +1246,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1257,11 +1267,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1276,7 +1286,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1286,17 +1296,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1305,16 +1315,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1324,12 +1329,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1345,11 +1350,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1364,7 +1369,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1374,17 +1379,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1402,7 +1407,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1412,12 +1417,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1433,11 +1438,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1452,7 +1457,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1462,17 +1467,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1485,7 +1490,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1495,12 +1500,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1516,11 +1521,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1535,7 +1540,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1545,17 +1550,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1573,7 +1578,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1583,12 +1588,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1604,11 +1609,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1623,7 +1628,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1633,17 +1638,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1652,16 +1657,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1671,12 +1676,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1692,11 +1697,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1711,7 +1716,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1721,17 +1726,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1740,11 +1745,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1754,12 +1764,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1775,11 +1785,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1794,7 +1804,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1804,17 +1814,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1823,11 +1833,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1837,12 +1852,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1858,11 +1873,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1887,17 +1902,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1920,12 +1935,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1941,11 +1956,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1975,12 +1990,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1989,7 +2004,12 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2003,12 +2023,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2024,11 +2044,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2058,12 +2078,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2091,12 +2111,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2112,11 +2132,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2131,7 +2151,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2141,17 +2161,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2160,11 +2180,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2174,12 +2199,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2195,11 +2220,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2214,7 +2239,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2224,17 +2249,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2243,16 +2268,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2262,12 +2282,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2283,11 +2303,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2302,7 +2322,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2312,17 +2332,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2331,11 +2351,16 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2345,12 +2370,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2366,11 +2391,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2385,7 +2410,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2395,17 +2420,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2423,7 +2448,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2433,12 +2458,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2454,11 +2479,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2483,17 +2508,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2516,12 +2541,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2537,11 +2562,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2556,7 +2581,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2566,17 +2591,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2585,11 +2610,16 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2599,12 +2629,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2620,11 +2650,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2654,12 +2684,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2687,12 +2717,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2708,11 +2738,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2727,7 +2757,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2737,17 +2767,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2760,7 +2790,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2770,12 +2800,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2791,11 +2821,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2810,7 +2840,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2820,17 +2850,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2848,7 +2878,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2858,12 +2888,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2879,11 +2909,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2908,17 +2938,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2936,7 +2966,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2946,12 +2976,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2967,11 +2997,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2986,7 +3016,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2996,17 +3026,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3015,11 +3045,16 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3029,12 +3064,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3050,11 +3085,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3069,7 +3104,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3079,17 +3114,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3098,11 +3133,16 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3112,12 +3152,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3133,11 +3173,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3152,7 +3192,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3162,17 +3202,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3181,16 +3221,16 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9,10</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3200,12 +3240,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3221,11 +3261,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3240,7 +3280,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3250,17 +3290,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3273,7 +3313,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3283,12 +3323,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3304,11 +3344,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3338,12 +3378,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3371,12 +3411,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3392,11 +3432,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3426,12 +3466,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3459,12 +3499,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3480,11 +3520,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3499,7 +3539,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3509,17 +3549,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3537,7 +3577,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3547,12 +3587,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3568,11 +3608,11 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3587,7 +3627,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3597,17 +3637,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3616,16 +3656,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3635,12 +3670,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3656,11 +3691,11 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3685,17 +3720,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3718,12 +3753,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3739,11 +3774,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3758,7 +3793,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3768,17 +3803,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3787,11 +3822,16 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3801,12 +3841,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3822,11 +3862,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3841,7 +3881,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3851,17 +3891,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3879,7 +3919,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3889,12 +3929,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3910,11 +3950,11 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3929,7 +3969,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3939,17 +3979,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3958,16 +3998,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3977,12 +4012,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3998,11 +4033,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4017,7 +4052,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4027,17 +4062,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4046,11 +4081,16 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4060,12 +4100,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4081,11 +4121,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4100,7 +4140,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4110,17 +4150,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4138,7 +4178,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4148,12 +4188,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4169,11 +4209,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4188,7 +4228,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4198,17 +4238,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4217,16 +4257,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4236,12 +4271,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4257,11 +4292,11 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4276,7 +4311,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4286,17 +4321,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4314,7 +4349,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4324,12 +4359,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4345,11 +4380,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4364,7 +4399,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4374,17 +4409,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4393,16 +4428,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4412,12 +4442,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4433,11 +4463,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4452,7 +4482,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4462,17 +4492,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4485,7 +4515,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4495,12 +4525,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4516,11 +4546,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4535,7 +4565,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4545,17 +4575,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4564,16 +4594,11 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4583,12 +4608,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4604,11 +4629,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4623,7 +4648,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4633,17 +4658,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4661,7 +4686,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4671,12 +4696,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4692,11 +4717,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4711,7 +4736,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4721,17 +4746,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4740,16 +4765,16 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.3888888888888889</v>
+        <v>0</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4759,12 +4784,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4780,11 +4805,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4799,7 +4824,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4809,17 +4834,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4828,16 +4853,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4847,12 +4867,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4868,11 +4888,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4887,7 +4907,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4897,17 +4917,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4916,16 +4936,11 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>9,10,11,12,13,14,15,16</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4935,12 +4950,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4956,11 +4971,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4975,7 +4990,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4985,17 +5000,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5013,7 +5028,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5023,12 +5038,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5044,11 +5059,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5073,17 +5088,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5106,12 +5121,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5127,11 +5142,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5146,7 +5161,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5156,17 +5171,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>yanxinyu</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>闫欣雨</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5175,16 +5190,11 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5194,12 +5204,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>yanxinyu</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>闫欣雨</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5215,11 +5225,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5234,7 +5244,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5244,17 +5254,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5263,16 +5273,11 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5282,12 +5287,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5303,11 +5308,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5332,17 +5337,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5351,7 +5356,12 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5365,12 +5375,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5386,11 +5396,11 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5405,7 +5415,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5415,17 +5425,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5443,7 +5453,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5453,12 +5463,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5474,11 +5484,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5493,7 +5503,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5503,17 +5513,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5531,7 +5541,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5541,12 +5551,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5562,11 +5572,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5596,12 +5606,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5610,11 +5620,11 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5629,12 +5639,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5650,11 +5660,11 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5679,17 +5689,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5698,11 +5708,11 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5717,12 +5727,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5738,11 +5748,11 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5757,7 +5767,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5767,17 +5777,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5786,16 +5796,11 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5805,12 +5810,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5826,11 +5831,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5855,17 +5860,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5893,12 +5898,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5914,11 +5919,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5943,17 +5948,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5976,12 +5981,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -5997,11 +6002,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6016,7 +6021,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6026,17 +6031,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6054,7 +6059,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6064,12 +6069,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6085,11 +6090,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6104,7 +6109,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6114,17 +6119,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6133,11 +6138,16 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6147,12 +6157,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6168,11 +6178,11 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6197,17 +6207,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6216,11 +6226,11 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6235,12 +6245,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6256,11 +6266,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6275,7 +6285,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6285,17 +6295,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6304,11 +6314,16 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6318,12 +6333,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6339,11 +6354,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6358,7 +6373,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6368,17 +6383,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6396,7 +6411,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6406,12 +6421,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6427,11 +6442,11 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6461,12 +6476,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6475,12 +6490,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -6494,12 +6504,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6515,11 +6525,11 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6534,7 +6544,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6544,17 +6554,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6563,11 +6573,16 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6577,12 +6592,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6598,11 +6613,11 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6617,7 +6632,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6627,17 +6642,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6655,7 +6670,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6665,12 +6680,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6686,11 +6701,11 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6700,12 +6715,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>长期班</t>
+          <t>短期班</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6715,17 +6730,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6734,16 +6749,11 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -6753,12 +6763,12 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6774,11 +6784,11 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6793,7 +6803,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6803,17 +6813,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6822,16 +6832,11 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6841,12 +6846,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6862,11 +6867,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6881,7 +6886,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6891,17 +6896,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6910,16 +6915,11 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6950,11 +6950,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6998,16 +6998,11 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7017,12 +7012,12 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -7038,11 +7033,11 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7057,7 +7052,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7067,17 +7062,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7095,7 +7090,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7105,12 +7100,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -7119,6 +7114,353 @@
         </is>
       </c>
       <c r="R77" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>zhangshuoyan</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>张硕研</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>zhangshuoyan</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>张硕研</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>yangbolan</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>杨博岚</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>yangbolan</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>杨博岚</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>guoyajing</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>郭雅静</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>guoyajing</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>郭雅静</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>yanhuiqing</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>闫慧清</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>yanhuiqing</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>闫慧清</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -7135,7 +7477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7183,17 +7525,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -7204,22 +7546,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0.25</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="4">
@@ -7235,17 +7577,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -7256,22 +7598,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -7291,13 +7633,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -7313,7 +7655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -7334,22 +7676,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -7363,7 +7731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7382,7 +7750,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 9月16日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 10月8日</t>
         </is>
       </c>
     </row>
@@ -7456,110 +7824,110 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3" t="e">
-        <v>#N/A</v>
+        <v>0.6</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>重装五组</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>初一 汇总</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="F4" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0.8</v>
+      <c r="J4" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>初一 汇总</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="5" t="n">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>0.8</v>
+      <c r="I5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -7575,110 +7943,110 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0.4615384615384616</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>8</v>
-      </c>
       <c r="I6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>初三 汇总</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="J7" s="6" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>初三 汇总</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>0.6666666666666666</v>
+      <c r="J8" s="4" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="9">
@@ -7698,28 +8066,28 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="10">
@@ -7735,7 +8103,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -7751,131 +8119,135 @@
         <v>9</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>初二 汇总</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.4594594594594595</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.6486486486486487</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>新兵营-出</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>0.4545454545454545</v>
+      <c r="D13" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -7886,33 +8258,70 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>初中 汇总</t>
+          <t>新兵营 汇总</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="E14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.3452380952380952</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="I15" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="F14" s="6" t="n">
-        <v>0.3552631578947368</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0.6052631578947368</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>0.6521739130434783</v>
+      <c r="J15" s="6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0.5510204081632653</v>
       </c>
     </row>
   </sheetData>
@@ -7929,7 +8338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7992,7 +8401,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8043,7 +8452,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8094,7 +8503,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8119,12 +8528,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -8145,7 +8554,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8170,19 +8579,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -8196,7 +8605,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8221,19 +8630,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -8247,7 +8656,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8272,19 +8681,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -8298,7 +8707,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8323,19 +8732,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -8349,7 +8758,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8374,19 +8783,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8400,7 +8809,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8425,16 +8834,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -8451,7 +8860,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8476,16 +8885,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -8502,7 +8911,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8517,29 +8926,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -8553,7 +8962,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8568,22 +8977,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -8604,7 +9013,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8629,16 +9038,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -8655,7 +9064,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8680,12 +9089,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -8706,7 +9115,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8731,16 +9140,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8757,7 +9166,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8782,12 +9191,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -8808,7 +9217,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8833,12 +9242,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -8859,7 +9268,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8884,12 +9293,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -8910,7 +9319,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8935,19 +9344,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -8961,7 +9370,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8986,12 +9395,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -9012,7 +9421,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9037,12 +9446,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -9063,7 +9472,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9083,24 +9492,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -9114,7 +9523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9134,24 +9543,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -9165,7 +9574,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9185,24 +9594,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -9216,7 +9625,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9236,17 +9645,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -9267,7 +9676,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9292,19 +9701,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -9318,7 +9727,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9343,12 +9752,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -9369,7 +9778,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9394,19 +9803,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -9420,7 +9829,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9445,19 +9854,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -9471,7 +9880,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9496,19 +9905,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -9522,7 +9931,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9547,19 +9956,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -9573,7 +9982,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9588,29 +9997,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -9624,7 +10033,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9639,29 +10048,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -9675,7 +10084,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9690,22 +10099,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -9726,7 +10135,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9741,22 +10150,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -9777,7 +10186,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9792,29 +10201,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -9828,7 +10237,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9848,24 +10257,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -9879,7 +10288,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9899,17 +10308,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -9930,7 +10339,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9950,24 +10359,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -9981,7 +10390,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10001,17 +10410,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -10032,7 +10441,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10052,24 +10461,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -10083,7 +10492,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -10103,17 +10512,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -10134,7 +10543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10154,24 +10563,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -10185,7 +10594,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -10205,17 +10614,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -10236,7 +10645,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -10256,24 +10665,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -10287,7 +10696,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10307,17 +10716,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -10338,7 +10747,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10358,17 +10767,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -10389,7 +10798,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -10409,24 +10818,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -10440,7 +10849,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10460,24 +10869,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -10491,7 +10900,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10511,17 +10920,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -10542,7 +10951,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10562,24 +10971,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -10593,7 +11002,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10613,24 +11022,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -10644,7 +11053,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10664,24 +11073,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -10695,7 +11104,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10715,21 +11124,21 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -10746,7 +11155,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10761,29 +11170,29 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -10797,7 +11206,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10812,29 +11221,29 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -10848,7 +11257,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10863,22 +11272,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -10899,7 +11308,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10914,29 +11323,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -10950,7 +11359,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10965,29 +11374,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="H60" t="n">
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -11001,7 +11410,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11016,29 +11425,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -11052,7 +11461,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11067,26 +11476,26 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -11103,7 +11512,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11118,26 +11527,26 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -11154,7 +11563,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -11169,22 +11578,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -11205,7 +11614,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -11220,22 +11629,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -11256,7 +11665,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -11271,29 +11680,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -11307,7 +11716,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -11332,16 +11741,16 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -11358,7 +11767,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -11383,12 +11792,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -11409,7 +11818,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -11434,16 +11843,16 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -11460,7 +11869,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -11485,26 +11894,638 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>lukai</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>芦凯</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
         <v>1</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>lvxiaofei</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>吕晓菲</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>mahaonan01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>马浩楠</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
         <v>1</v>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>mengsinan</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>孟思楠</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>wanglu03</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>王璐</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>xuyuan01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>徐源</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>yangzhijie01</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>杨志杰</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>yeyanhong</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>野艳红</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>zhangbaohua01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>张宝华</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>zhangbingxin</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>张冰心</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>zhangxinchi</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>张心驰</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
         <v>23</v>
       </c>
     </row>
@@ -11519,7 +12540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11577,20 +12598,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -11601,28 +12625,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -11638,23 +12662,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6</v>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -11665,28 +12689,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -11706,19 +12730,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="7">
@@ -11734,20 +12758,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H7" t="n">
         <v>0.6666666666666666</v>
@@ -11761,28 +12785,60 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>新兵营-出</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>21</v>
-      </c>
-      <c r="E8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4545454545454545</v>
+      <c r="D9" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3333333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -690,17 +690,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,16 +709,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,12 +723,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -753,7 +748,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -768,7 +763,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -778,17 +773,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -806,7 +801,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,12 +811,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -841,7 +836,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -856,7 +851,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -866,17 +861,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -885,16 +880,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -904,12 +894,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -929,7 +919,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -944,7 +934,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -954,17 +944,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -973,11 +963,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -987,12 +982,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1012,7 +1007,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1037,17 +1032,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1056,7 +1051,12 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1120,17 +1120,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1315,11 +1315,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1329,12 +1334,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1354,7 +1359,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1369,7 +1374,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1379,17 +1384,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1398,16 +1403,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1467,17 +1467,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1486,7 +1486,12 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1500,12 +1505,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1525,7 +1530,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1540,7 +1545,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1550,17 +1555,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1578,7 +1583,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1588,12 +1593,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1613,7 +1618,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1628,7 +1633,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1638,17 +1643,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1657,16 +1662,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1731,12 +1731,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1814,17 +1814,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1833,16 +1833,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1985,17 +1985,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2004,16 +2004,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2023,12 +2018,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2048,7 +2043,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2063,7 +2058,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2073,17 +2068,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2092,16 +2087,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2111,12 +2101,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2136,7 +2126,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2151,7 +2141,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2161,17 +2151,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2180,16 +2170,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2199,12 +2184,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2224,7 +2209,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2239,7 +2224,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2249,17 +2234,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2268,11 +2253,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2282,12 +2272,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2307,7 +2297,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2322,7 +2312,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2332,17 +2322,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2360,7 +2350,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2370,12 +2360,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2395,7 +2385,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2410,7 +2400,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2420,17 +2410,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2439,16 +2429,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2458,12 +2443,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2483,7 +2468,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2508,17 +2493,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2527,7 +2512,12 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2541,12 +2531,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2566,7 +2556,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2581,7 +2571,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2591,17 +2581,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2619,7 +2609,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2629,12 +2619,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2654,7 +2644,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2669,7 +2659,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2679,17 +2669,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2698,16 +2688,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2717,12 +2707,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2742,7 +2732,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2757,7 +2747,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2767,17 +2757,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2786,11 +2776,16 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2800,12 +2795,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2825,7 +2820,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2840,7 +2835,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2850,17 +2845,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2878,7 +2873,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2888,12 +2883,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2913,7 +2908,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2928,7 +2923,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2938,17 +2933,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2966,7 +2961,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2976,12 +2971,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3001,7 +2996,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3016,7 +3011,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3026,17 +3021,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3045,16 +3040,16 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3064,12 +3059,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3089,7 +3084,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3104,7 +3099,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3114,17 +3109,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3142,7 +3137,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3152,12 +3147,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3177,7 +3172,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3192,7 +3187,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3202,17 +3197,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3221,16 +3216,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3240,12 +3230,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3265,7 +3255,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3290,17 +3280,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3323,12 +3313,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3348,7 +3338,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3378,12 +3368,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3411,12 +3401,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3436,7 +3426,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3451,7 +3441,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3461,17 +3451,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3489,7 +3479,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3499,12 +3489,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3524,7 +3514,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3539,7 +3529,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3549,17 +3539,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3577,7 +3567,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3587,12 +3577,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3612,7 +3602,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3627,7 +3617,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3637,17 +3627,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3656,11 +3646,16 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3670,12 +3665,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3695,7 +3690,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3720,17 +3715,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3753,12 +3748,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3778,7 +3773,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3803,17 +3798,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3822,11 +3817,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3841,12 +3836,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3866,7 +3861,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3881,7 +3876,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3891,17 +3886,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3919,7 +3914,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3929,12 +3924,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3954,7 +3949,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3969,7 +3964,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3979,17 +3974,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3998,11 +3993,16 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4150,17 +4150,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4238,17 +4238,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4257,11 +4257,16 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4271,12 +4276,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4296,7 +4301,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4311,7 +4316,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4321,17 +4326,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4349,7 +4354,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4359,12 +4364,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4384,7 +4389,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4399,7 +4404,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4409,17 +4414,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4428,11 +4433,16 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4442,12 +4452,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4467,7 +4477,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4482,7 +4492,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4492,17 +4502,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4515,7 +4525,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4525,12 +4535,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4550,7 +4560,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4565,7 +4575,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4575,17 +4585,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4594,11 +4604,16 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4608,12 +4623,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4633,7 +4648,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4648,7 +4663,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4658,17 +4673,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4686,7 +4701,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4696,12 +4711,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4721,7 +4736,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4746,17 +4761,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4765,12 +4780,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4784,12 +4794,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4809,7 +4819,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4834,17 +4844,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4867,12 +4877,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4892,7 +4902,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4922,12 +4932,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4936,7 +4946,12 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4950,12 +4965,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4975,7 +4990,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4990,7 +5005,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5000,17 +5015,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5028,7 +5043,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5038,12 +5053,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5063,7 +5078,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5078,7 +5093,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5088,17 +5103,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5107,11 +5122,16 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5121,12 +5141,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5146,7 +5166,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5161,7 +5181,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5171,17 +5191,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5194,7 +5214,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5204,12 +5224,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5229,7 +5249,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5244,7 +5264,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5254,17 +5274,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5273,11 +5293,16 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5287,12 +5312,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5312,7 +5337,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5337,17 +5362,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5356,12 +5381,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5375,12 +5395,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5400,7 +5420,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5415,7 +5435,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5425,17 +5445,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5453,7 +5473,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5463,12 +5483,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5488,7 +5508,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5503,7 +5523,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5513,17 +5533,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5532,16 +5552,11 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5551,12 +5566,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5576,7 +5591,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5591,7 +5606,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5601,17 +5616,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5620,16 +5635,16 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>6,7,8,9</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5639,12 +5654,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5664,7 +5679,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5679,7 +5694,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5689,17 +5704,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5708,16 +5723,16 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.05555555555555555</v>
+        <v>0</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5727,12 +5742,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5752,7 +5767,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5777,17 +5792,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5810,12 +5825,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5835,7 +5850,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5850,7 +5865,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5860,17 +5875,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5879,16 +5894,11 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5898,12 +5908,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5923,7 +5933,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5938,7 +5948,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5948,17 +5958,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5971,7 +5981,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5981,12 +5991,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6006,7 +6016,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6021,7 +6031,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6031,17 +6041,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6059,7 +6069,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6069,12 +6079,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6094,7 +6104,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6109,7 +6119,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6119,17 +6129,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6138,16 +6148,11 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6157,12 +6162,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6182,7 +6187,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6197,7 +6202,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6207,17 +6212,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6226,16 +6231,11 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6295,17 +6295,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6314,16 +6314,11 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6333,12 +6328,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6358,7 +6353,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6383,17 +6378,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6421,12 +6416,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6446,7 +6441,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6461,7 +6456,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6471,17 +6466,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6490,11 +6485,16 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6554,17 +6554,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6573,16 +6573,11 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6592,12 +6587,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6617,7 +6612,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6642,17 +6637,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6680,12 +6675,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6705,7 +6700,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6749,7 +6744,12 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>20,21,22,23</t>
+        </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6832,11 +6832,16 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6846,12 +6851,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6871,7 +6876,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6901,12 +6906,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6915,7 +6920,12 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -6929,12 +6939,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6954,7 +6964,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6979,17 +6989,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7012,12 +7022,12 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -7037,7 +7047,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7052,7 +7062,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7062,17 +7072,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7081,16 +7091,11 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7100,12 +7105,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -7125,7 +7130,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7140,7 +7145,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7150,17 +7155,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7169,11 +7174,16 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7183,12 +7193,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7208,7 +7218,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7233,17 +7243,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7252,12 +7262,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -7271,12 +7276,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7296,7 +7301,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7311,7 +7316,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7321,17 +7326,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7349,7 +7354,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -7359,12 +7364,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7384,7 +7389,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7414,12 +7419,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7447,12 +7452,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7532,10 +7537,10 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3">
@@ -7584,10 +7589,10 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -7750,7 +7755,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 10月8日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 10月9日</t>
         </is>
       </c>
     </row>
@@ -7831,25 +7836,25 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="4">
@@ -7868,25 +7873,25 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>10</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -7918,16 +7923,16 @@
         <v>11</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="6">
@@ -7950,10 +7955,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10</v>
@@ -7962,13 +7967,13 @@
         <v>6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>0.6</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -7987,25 +7992,25 @@
         <v>21</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>21</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.6</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="8">
@@ -8303,25 +8308,25 @@
         <v>84</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>84</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6309523809523809</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.5510204081632653</v>
+        <v>0.5471698113207547</v>
       </c>
     </row>
   </sheetData>
@@ -8338,7 +8343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8401,7 +8406,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8452,7 +8457,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8503,7 +8508,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8537,7 +8542,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -8554,7 +8559,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8605,7 +8610,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8656,7 +8661,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8707,7 +8712,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8758,7 +8763,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8809,7 +8814,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8860,7 +8865,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8911,7 +8916,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8962,7 +8967,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8996,10 +9001,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -9013,7 +9018,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9064,7 +9069,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9101,7 +9106,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -9115,7 +9120,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9166,7 +9171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9200,10 +9205,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -9217,7 +9222,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9251,7 +9256,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -9268,7 +9273,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9319,7 +9324,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9370,7 +9375,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9421,7 +9426,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9472,7 +9477,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9523,7 +9528,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9574,7 +9579,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9625,7 +9630,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9676,7 +9681,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9727,7 +9732,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9778,7 +9783,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9829,7 +9834,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9880,7 +9885,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9931,7 +9936,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9968,7 +9973,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -9982,7 +9987,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -10033,7 +10038,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -10084,7 +10089,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10135,7 +10140,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10186,7 +10191,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10237,7 +10242,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10288,7 +10293,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10339,7 +10344,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10390,7 +10395,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10441,7 +10446,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10492,7 +10497,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -10543,7 +10548,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10594,7 +10599,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -10645,7 +10650,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -10696,7 +10701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10747,7 +10752,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10798,7 +10803,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -10849,7 +10854,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10900,7 +10905,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10951,7 +10956,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -11002,7 +11007,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -11053,7 +11058,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -11104,7 +11109,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -11155,7 +11160,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11206,7 +11211,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11257,7 +11262,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11308,7 +11313,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11359,7 +11364,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11410,7 +11415,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11461,7 +11466,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11512,7 +11517,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11563,7 +11568,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -11614,7 +11619,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -11665,7 +11670,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -11680,22 +11685,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -11716,7 +11721,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -11741,19 +11746,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -11767,7 +11772,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -11792,19 +11797,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -11818,7 +11823,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -11843,16 +11848,16 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -11869,7 +11874,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -11894,16 +11899,16 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -11920,7 +11925,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -11945,16 +11950,16 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -11971,7 +11976,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -11996,16 +12001,16 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -12022,7 +12027,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -12047,12 +12052,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -12073,7 +12078,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -12098,16 +12103,16 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -12124,7 +12129,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12149,19 +12154,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -12175,7 +12180,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -12200,19 +12205,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -12226,7 +12231,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -12251,16 +12256,16 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -12277,7 +12282,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12302,12 +12307,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -12328,7 +12333,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -12353,19 +12358,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -12379,7 +12384,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -12404,19 +12409,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="H80" t="n">
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -12430,7 +12435,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12455,16 +12460,16 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -12475,57 +12480,6 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>zhangxinchi</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>张心驰</t>
-        </is>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
         <v>23</v>
       </c>
     </row>
@@ -12605,16 +12559,16 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="3">
@@ -12637,16 +12591,16 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -12672,13 +12626,13 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0.6</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">

--- a/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,7 +577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,12 +621,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -640,12 +635,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -665,7 +660,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -680,7 +675,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -690,17 +685,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,11 +704,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,7</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -773,17 +773,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>wujinxian</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>武金贤</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>wujinxian</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>武金贤</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -861,17 +861,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -880,11 +880,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -894,12 +899,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -919,7 +924,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -934,7 +939,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -944,17 +949,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -972,7 +977,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -982,12 +987,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1007,7 +1012,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1022,7 +1027,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1032,17 +1037,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>wanganran</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>王安冉</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1060,7 +1065,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1070,12 +1075,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>wanganran</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>王安冉</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1095,7 +1100,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1110,7 +1115,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1120,17 +1125,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1148,7 +1153,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1158,12 +1163,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1198,7 +1203,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1208,17 +1213,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1236,7 +1241,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1246,12 +1251,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1271,7 +1276,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1286,7 +1291,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1296,17 +1301,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1315,16 +1320,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>shanhaotian</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>单昊天</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1403,11 +1403,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1417,12 +1422,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>shanhaotian</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>单昊天</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1472,12 +1477,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1486,11 +1491,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>16,17</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1505,12 +1510,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1530,7 +1535,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1545,7 +1550,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1555,17 +1560,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1583,7 +1588,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1593,12 +1598,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1618,7 +1623,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1633,7 +1638,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1643,17 +1648,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1666,7 +1671,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1676,12 +1681,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1701,7 +1706,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1716,7 +1721,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1726,17 +1731,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1754,7 +1759,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1764,12 +1769,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1789,7 +1794,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1804,7 +1809,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1814,17 +1819,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1833,16 +1838,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1852,12 +1857,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1877,7 +1882,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1892,7 +1897,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1902,17 +1907,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1925,7 +1930,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1935,12 +1940,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1960,7 +1965,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1975,7 +1980,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1985,17 +1990,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2004,11 +2009,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2018,12 +2028,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2043,7 +2053,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2058,7 +2068,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2068,17 +2078,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2091,7 +2101,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2101,12 +2111,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2126,7 +2136,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2156,12 +2166,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2184,12 +2194,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2209,7 +2219,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2224,7 +2234,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2234,17 +2244,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2262,7 +2272,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2272,12 +2282,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2297,7 +2307,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2312,7 +2322,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2322,17 +2332,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2341,16 +2351,11 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2360,12 +2365,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2385,7 +2390,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2410,17 +2415,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2443,12 +2448,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2468,7 +2473,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2493,17 +2498,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2512,12 +2517,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2581,17 +2581,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2600,16 +2600,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2619,12 +2614,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2644,7 +2639,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2659,7 +2654,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2669,17 +2664,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2688,16 +2683,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2707,12 +2702,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2732,7 +2727,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2762,12 +2757,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2776,12 +2771,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2795,12 +2785,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2820,7 +2810,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2835,7 +2825,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2845,17 +2835,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2864,16 +2854,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2883,12 +2868,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2908,7 +2893,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2923,7 +2908,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2933,17 +2918,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2961,7 +2946,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2971,12 +2956,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2996,7 +2981,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3011,7 +2996,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3021,17 +3006,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3049,7 +3034,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3059,12 +3044,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3084,7 +3069,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3114,12 +3099,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3147,12 +3132,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3172,7 +3157,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3187,7 +3172,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3197,17 +3182,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3216,11 +3201,16 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,23</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3230,12 +3220,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3255,7 +3245,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3270,7 +3260,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3280,17 +3270,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3299,11 +3289,16 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3313,12 +3308,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3338,7 +3333,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3363,17 +3358,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3401,12 +3396,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3426,7 +3421,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3441,7 +3436,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3451,17 +3446,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3470,16 +3465,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3489,12 +3479,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3514,7 +3504,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3539,17 +3529,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3558,12 +3548,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3577,12 +3562,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3602,7 +3587,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3617,7 +3602,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3627,17 +3612,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3655,7 +3640,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3665,12 +3650,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3690,7 +3675,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3705,7 +3690,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3715,17 +3700,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3734,11 +3719,16 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3748,12 +3738,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3773,7 +3763,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3821,7 +3811,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3861,7 +3851,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3876,7 +3866,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3886,17 +3876,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3905,16 +3895,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3924,12 +3909,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3949,7 +3934,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3979,12 +3964,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4012,12 +3997,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4037,7 +4022,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4067,12 +4052,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4081,12 +4066,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -4100,12 +4080,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4125,7 +4105,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4140,7 +4120,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4150,17 +4130,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4169,16 +4149,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4188,12 +4163,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4213,7 +4188,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4228,7 +4203,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4238,17 +4213,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4266,7 +4241,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4276,12 +4251,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4301,7 +4276,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4316,7 +4291,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4326,17 +4301,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4354,7 +4329,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4364,12 +4339,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4389,7 +4364,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4404,7 +4379,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4414,17 +4389,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>jiziao</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>季子傲</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4442,7 +4417,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4452,12 +4427,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>jiziao</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>季子傲</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4477,7 +4452,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4502,17 +4477,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4521,7 +4496,12 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4535,12 +4515,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -4560,7 +4540,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4575,7 +4555,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4585,17 +4565,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4604,16 +4584,11 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4623,12 +4598,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4648,7 +4623,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4663,7 +4638,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4673,17 +4648,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4701,7 +4676,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4711,12 +4686,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4736,7 +4711,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4751,7 +4726,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4761,17 +4736,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4780,11 +4755,16 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4794,12 +4774,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4819,7 +4799,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4834,7 +4814,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4844,17 +4824,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4863,11 +4843,16 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4877,12 +4862,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4902,7 +4887,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4917,7 +4902,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4927,17 +4912,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4946,16 +4931,16 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11</t>
+          <t>6,7,8,12</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4965,12 +4950,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -4990,7 +4975,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5005,7 +4990,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5015,17 +5000,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5043,7 +5028,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5053,12 +5038,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5078,7 +5063,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5108,12 +5093,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5141,12 +5126,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5166,7 +5151,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5181,7 +5166,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5191,17 +5176,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5210,11 +5195,16 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5224,12 +5214,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5249,7 +5239,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5264,7 +5254,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5274,17 +5264,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5302,7 +5292,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5312,12 +5302,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5337,7 +5327,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5352,7 +5342,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5362,17 +5352,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5381,11 +5371,16 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5395,12 +5390,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5420,7 +5415,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5450,12 +5445,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>wangzi</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>王姿</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5483,12 +5478,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>wangzi</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>王姿</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5508,7 +5503,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5533,17 +5528,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5552,7 +5547,12 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5616,17 +5616,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5635,16 +5635,11 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5654,12 +5649,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5679,7 +5674,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5694,7 +5689,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5704,17 +5699,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5732,7 +5727,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5742,12 +5737,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -5767,7 +5762,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5792,17 +5787,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5825,12 +5820,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5850,7 +5845,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5875,17 +5870,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5894,7 +5889,12 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5958,17 +5958,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6148,7 +6148,12 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -6162,12 +6167,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -6187,7 +6192,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6202,7 +6207,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6212,17 +6217,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6231,11 +6236,16 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -6245,12 +6255,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6270,7 +6280,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6300,12 +6310,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6328,12 +6338,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6353,7 +6363,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6368,7 +6378,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6378,17 +6388,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6406,7 +6416,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6416,12 +6426,12 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6441,7 +6451,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6456,7 +6466,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6466,17 +6476,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6485,16 +6495,16 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6504,12 +6514,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6529,7 +6539,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6559,12 +6569,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6587,12 +6597,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -6612,7 +6622,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6627,7 +6637,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6637,17 +6647,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6665,7 +6675,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6675,12 +6685,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -6700,7 +6710,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6715,7 +6725,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6725,17 +6735,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6744,16 +6754,16 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -6763,12 +6773,12 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -6788,7 +6798,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6803,7 +6813,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6813,17 +6823,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6832,16 +6842,11 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6851,12 +6856,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6876,7 +6881,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6891,7 +6896,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6901,17 +6906,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6920,16 +6925,11 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7091,11 +7091,16 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7105,12 +7110,12 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -7130,7 +7135,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7145,7 +7150,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7155,17 +7160,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -7174,16 +7179,11 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7243,17 +7243,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>jitansi</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>纪覃思</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>jitansi</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>纪覃思</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7414,17 +7414,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -7442,30 +7442,548 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>zhangxinchi</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>张心驰</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>guoyajing</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>郭雅静</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>guoyajing</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>郭雅静</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>yangjiaxue</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>杨佳雪</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>liyang06</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>李洋</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>yangjiaxue</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>杨佳雪</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>anyixuan</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>安怡宣</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>anyixuan</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>安怡宣</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>chenlihui</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>陈利辉</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>chenlihui</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>陈利辉</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>yangbolan</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>杨博岚</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>yangbolan</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>杨博岚</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>秋拾</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>shenyuxin</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>沈宇心</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>shenyuxin</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>沈宇心</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -7537,10 +8055,10 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -7563,10 +8081,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="4">
@@ -7716,13 +8234,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -7755,7 +8273,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 10月9日</t>
+          <t>个微-风灵全天在线率及爱芯授权功能正常率（石家庄初短） 10月11日</t>
         </is>
       </c>
     </row>
@@ -7836,10 +8354,10 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>10</v>
@@ -7848,13 +8366,13 @@
         <v>7</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -7873,10 +8391,10 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>10</v>
@@ -7885,13 +8403,13 @@
         <v>7</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="5">
@@ -7914,25 +8432,25 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="J5" s="4" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -7992,25 +8510,25 @@
         <v>21</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>21</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -8231,16 +8749,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>9</v>
@@ -8249,7 +8767,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>0.3333333333333333</v>
@@ -8268,16 +8786,16 @@
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>9</v>
@@ -8286,7 +8804,7 @@
         <v>3</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0.3333333333333333</v>
@@ -8305,28 +8823,28 @@
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.5471698113207547</v>
+        <v>0.5925925925925926</v>
       </c>
     </row>
   </sheetData>
@@ -8343,7 +8861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8406,7 +8924,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8457,7 +8975,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8508,7 +9026,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8559,7 +9077,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8610,7 +9128,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8661,7 +9179,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8712,7 +9230,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8763,7 +9281,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8814,7 +9332,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8865,7 +9383,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8902,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -8916,7 +9434,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8967,7 +9485,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9018,7 +9536,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9069,7 +9587,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9120,7 +9638,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9171,7 +9689,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9222,7 +9740,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9259,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -9273,7 +9791,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9324,7 +9842,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9375,7 +9893,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9426,7 +9944,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9460,10 +9978,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -9477,7 +9995,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9528,7 +10046,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9579,7 +10097,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9630,7 +10148,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9681,7 +10199,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9732,7 +10250,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9783,7 +10301,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9834,7 +10352,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9885,7 +10403,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9936,7 +10454,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9987,7 +10505,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -10038,7 +10556,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -10089,7 +10607,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10140,7 +10658,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10191,7 +10709,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10242,7 +10760,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10293,7 +10811,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10344,7 +10862,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10395,7 +10913,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10446,7 +10964,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10497,7 +11015,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -10548,7 +11066,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10599,7 +11117,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -10650,7 +11168,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -10701,7 +11219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10752,7 +11270,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10803,7 +11321,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -10854,7 +11372,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10905,7 +11423,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10956,7 +11474,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -11007,7 +11525,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -11058,7 +11576,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -11109,7 +11627,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -11160,7 +11678,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -11211,7 +11729,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -11262,7 +11780,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11313,7 +11831,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11364,7 +11882,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11415,7 +11933,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11466,7 +11984,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11517,7 +12035,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11568,7 +12086,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -11619,7 +12137,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -11670,7 +12188,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -11685,22 +12203,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -11721,7 +12239,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -11746,19 +12264,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -11772,7 +12290,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -11797,19 +12315,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -11823,7 +12341,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -11848,16 +12366,16 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -11874,7 +12392,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -11899,16 +12417,16 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -11925,7 +12443,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -11950,16 +12468,16 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -11976,7 +12494,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -12001,16 +12519,16 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -12027,7 +12545,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -12052,12 +12570,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -12078,7 +12596,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -12103,16 +12621,16 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -12129,7 +12647,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12154,19 +12672,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -12180,7 +12698,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -12205,19 +12723,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -12231,7 +12749,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -12256,16 +12774,16 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -12282,7 +12800,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12307,12 +12825,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -12333,7 +12851,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -12358,19 +12876,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -12384,7 +12902,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -12409,19 +12927,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="H80" t="n">
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -12435,7 +12953,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12460,16 +12978,16 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -12480,6 +12998,57 @@
         </is>
       </c>
       <c r="K81" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>zhangxinchi</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>张心驰</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
         <v>23</v>
       </c>
     </row>
@@ -12562,13 +13131,13 @@
         <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>0.7</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="3">
@@ -12591,16 +13160,16 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
         <v>7</v>
       </c>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="4">
@@ -12780,7 +13349,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
         <v>9</v>
@@ -12789,7 +13358,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.3333333333333333</v>
